--- a/data/wsjf_features.xlsx
+++ b/data/wsjf_features.xlsx
@@ -526,25 +526,25 @@
         <v>26</v>
       </c>
       <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -561,25 +561,25 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -595,26 +595,11 @@
       <c r="D4" t="s">
         <v>28</v>
       </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
       <c r="I4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>3.33</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -630,26 +615,11 @@
       <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="E5">
-        <v>13</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>8</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
       <c r="I5">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>14.5</v>
-      </c>
-      <c r="K5">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
